--- a/data/trans_orig/IP36A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP36A-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6044</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38280</t>
+          <t>38573</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51020</t>
+          <t>51648</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92491</t>
+          <t>91955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97946</t>
+          <t>97858</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13704</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9898</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>22396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90291</t>
+          <t>90093</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99757</t>
+          <t>99526</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95675</t>
+          <t>95514</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>104054</t>
+          <t>104000</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>189927</t>
+          <t>189485</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>201983</t>
+          <t>201642</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10781</t>
+          <t>10836</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15198</t>
+          <t>14420</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61297</t>
+          <t>61242</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69354</t>
+          <t>69320</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49601</t>
+          <t>49832</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55310</t>
+          <t>55305</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113449</t>
+          <t>114227</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123360</t>
+          <t>123852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12010</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15531</t>
+          <t>15120</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11564</t>
+          <t>12266</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24687</t>
+          <t>24270</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>70866</t>
+          <t>70701</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>78998</t>
+          <t>78983</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79648</t>
+          <t>80059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>89278</t>
+          <t>89232</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153367</t>
+          <t>153784</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>166490</t>
+          <t>165788</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,11%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15541</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30403</t>
+          <t>30572</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29705</t>
+          <t>30825</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35070</t>
+          <t>35680</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55613</t>
+          <t>55861</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>271085</t>
+          <t>270916</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>285947</t>
+          <t>285661</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>285925</t>
+          <t>284805</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>299997</t>
+          <t>299769</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>561505</t>
+          <t>561257</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>582048</t>
+          <t>581438</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>5040</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14588</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>12528</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>10899</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23263</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67454</t>
+          <t>67970</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77041</t>
+          <t>77002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70057</t>
+          <t>70268</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78980</t>
+          <t>79101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141868</t>
+          <t>141575</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>154237</t>
+          <t>153939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17340</t>
+          <t>18036</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21875</t>
+          <t>21541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>18408</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35238</t>
+          <t>34437</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112498</t>
+          <t>111802</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>123568</t>
+          <t>123092</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121600</t>
+          <t>121934</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>133952</t>
+          <t>133561</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>238075</t>
+          <t>238876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>254309</t>
+          <t>254905</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>9898</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12246</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>7841</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18918</t>
+          <t>18632</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72555</t>
+          <t>72687</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79932</t>
+          <t>80115</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68366</t>
+          <t>68518</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76720</t>
+          <t>76596</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144279</t>
+          <t>144565</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155664</t>
+          <t>155356</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20090</t>
+          <t>19527</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>7942</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18932</t>
+          <t>19358</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18480</t>
+          <t>19109</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33602</t>
+          <t>35458</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69647</t>
+          <t>70210</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81257</t>
+          <t>81389</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>87269</t>
+          <t>86843</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>98417</t>
+          <t>98259</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>162336</t>
+          <t>160480</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>177458</t>
+          <t>176829</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29687</t>
+          <t>29964</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48926</t>
+          <t>48322</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32288</t>
+          <t>32162</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51979</t>
+          <t>53201</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67089</t>
+          <t>66616</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>94406</t>
+          <t>95421</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>335276</t>
+          <t>335880</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>354515</t>
+          <t>354238</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>361104</t>
+          <t>359882</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>380795</t>
+          <t>380921</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>702879</t>
+          <t>701864</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>730196</t>
+          <t>730669</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,64%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>12583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61577</t>
+          <t>60900</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67556</t>
+          <t>67452</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53062</t>
+          <t>53287</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59198</t>
+          <t>59324</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117369</t>
+          <t>117244</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125928</t>
+          <t>125704</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19895</t>
+          <t>18909</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12215</t>
+          <t>12010</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25243</t>
+          <t>25211</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91828</t>
+          <t>91691</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98779</t>
+          <t>98452</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>104353</t>
+          <t>105339</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>116042</t>
+          <t>116401</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>199734</t>
+          <t>199766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212762</t>
+          <t>212967</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17795</t>
+          <t>17927</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19526</t>
+          <t>18981</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18170</t>
+          <t>17976</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32392</t>
+          <t>33665</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77869</t>
+          <t>77737</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87969</t>
+          <t>88326</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75583</t>
+          <t>76128</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87563</t>
+          <t>87318</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158381</t>
+          <t>157108</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>172603</t>
+          <t>172797</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,58%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4865</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14903</t>
+          <t>14591</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22665</t>
+          <t>22636</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17743</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34992</t>
+          <t>33450</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76515</t>
+          <t>76827</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86553</t>
+          <t>86117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61470</t>
+          <t>61499</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74221</t>
+          <t>73786</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>140561</t>
+          <t>142103</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>157810</t>
+          <t>158006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22052</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38235</t>
+          <t>38589</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34212</t>
+          <t>35004</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55659</t>
+          <t>55841</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62753</t>
+          <t>61533</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89150</t>
+          <t>89457</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>318887</t>
+          <t>318533</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>335070</t>
+          <t>334672</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>308348</t>
+          <t>308166</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>329795</t>
+          <t>329003</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>631980</t>
+          <t>631673</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>658377</t>
+          <t>659597</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6576</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>9601</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13017</t>
+          <t>12824</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17610</t>
+          <t>17429</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11956</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17272</t>
+          <t>17365</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26343</t>
+          <t>27003</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33958</t>
+          <t>33949</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12204</t>
+          <t>12325</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12010</t>
+          <t>11294</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24605</t>
+          <t>23385</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17495</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32842</t>
+          <t>32370</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38029</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46272</t>
+          <t>46297</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37532</t>
+          <t>38752</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50127</t>
+          <t>50843</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79649</t>
+          <t>80121</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>94996</t>
+          <t>94689</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10212</t>
+          <t>10627</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25828</t>
+          <t>26230</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5541</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16665</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>19269</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40108</t>
+          <t>38748</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40968</t>
+          <t>40566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56584</t>
+          <t>56169</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48062</t>
+          <t>49004</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59186</t>
+          <t>59268</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>91414</t>
+          <t>92774</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111607</t>
+          <t>112253</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23666</t>
+          <t>23852</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27496</t>
+          <t>26047</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21261</t>
+          <t>20273</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43836</t>
+          <t>45168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101390</t>
+          <t>101204</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118655</t>
+          <t>118564</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>84997</t>
+          <t>86446</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101014</t>
+          <t>101223</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>193713</t>
+          <t>192381</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>216288</t>
+          <t>217276</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26728</t>
+          <t>28086</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56756</t>
+          <t>55108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38180</t>
+          <t>37838</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61063</t>
+          <t>60364</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70319</t>
+          <t>70261</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109177</t>
+          <t>107481</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203522</t>
+          <t>205170</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>233550</t>
+          <t>232192</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196825</t>
+          <t>197524</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>219708</t>
+          <t>220050</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>408990</t>
+          <t>410686</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>447848</t>
+          <t>447906</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP36A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP36A-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,67 +728,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4965</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,87%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>1107</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3966</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3369</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,6%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1413</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4348</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>54583</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>51031</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>55996</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,48%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,13%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>41432</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>38573</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>39170</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>42539</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,4%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,68%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>92,08%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>54583</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>51648</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>55996</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,48%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>92,24%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>145</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>91955</t>
+          <t>91726</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97858</t>
+          <t>97816</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>55996</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>55996</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>55996</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>42539</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>42539</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>42539</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>55996</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>55996</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>55996</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7279</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3455</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>12656</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,75%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,73%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>8272</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4469</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13902</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4563</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14289</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,95%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,37%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7279</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3886</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>12372</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,75%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10239</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22396</t>
+          <t>22291</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>100607</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>95230</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>104431</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,25%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,27%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,8%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>95723</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>90093</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>99526</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>89706</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>99432</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,05%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,7%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>100607</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>95514</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>104000</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,25%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>189485</t>
+          <t>189590</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>201642</t>
+          <t>201727</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,21%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>107886</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>107886</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>107886</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>103995</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>103995</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>103995</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>107886</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>107886</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>107886</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,107 +1409,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3341</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1264</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7354</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5776</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2758</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10836</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10344</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>8,01%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>14,35%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>9117</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>4923</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>14626</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>15,03%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3341</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6738</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>11,91%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>9117</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>4795</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>14420</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -1522,107 +1522,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>53229</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>49216</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>55306</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,09%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66302</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>61242</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>69320</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>61734</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>69249</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>91,99%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>84,97%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>85,65%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>119530</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>114021</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>123724</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>92,91%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>88,63%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>96,17%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>53229</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>49832</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>55305</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,09%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>88,09%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>119530</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>114227</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>123852</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>92,91%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>88,79%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>96,27%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56570</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56570</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56570</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>72078</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>72078</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>72078</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>56570</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>56570</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>56570</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10092</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6202</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16468</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,6%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>7345</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3893</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12175</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3940</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12133</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,86%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>14,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10092</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5947</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>15120</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,6%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>12014</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24270</t>
+          <t>24860</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>85087</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>78711</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>88977</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,4%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>82,7%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>75531</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>70701</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>78983</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>70743</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>78936</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,14%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>85,31%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>85087</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>80059</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>89232</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,4%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153784</t>
+          <t>153194</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165788</t>
+          <t>166040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>95179</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>95179</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>95179</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>82876</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>82876</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>82876</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>95179</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>95179</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>95179</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>22125</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16332</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>30481</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,66%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>22499</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15827</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>30572</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>15685</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>30786</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>7,46%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>22125</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>15861</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>30825</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35680</t>
+          <t>35697</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55861</t>
+          <t>55657</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>293505</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>285149</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>299298</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,34%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,83%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>418</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>278989</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>270916</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>285661</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>270702</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>285803</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>92,54%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,86%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>441</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>293505</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>284805</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>299769</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,99%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>561257</t>
+          <t>561461</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>581438</t>
+          <t>581421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>315630</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>315630</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>315630</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>451</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>301488</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>301488</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>301488</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>315630</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>315630</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>315630</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6950</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3496</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11962</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,39%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,22%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,45%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>9024</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5040</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14072</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14862</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>11,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6950</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3695</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12528</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10899</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23263</t>
+          <t>23404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>75846</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>70834</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>79300</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,55%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,78%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>73018</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>67970</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>77002</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>67180</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>76715</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>89,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>75846</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>70268</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>79101</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,61%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>141575</t>
+          <t>141434</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>153939</t>
+          <t>154173</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82796</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82796</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82796</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>82042</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>82042</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>82042</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82796</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82796</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82796</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>15017</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10177</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>22227</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,47%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>10814</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6746</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18036</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6425</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16732</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>8,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,2%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>15017</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9914</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>21541</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>10,47%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34437</t>
+          <t>35104</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>128458</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>121248</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>133298</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>84,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,91%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>119024</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>111802</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>123092</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>113106</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>123413</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>91,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,8%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>128458</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>121934</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>133561</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>89,53%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>238876</t>
+          <t>238209</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>254905</t>
+          <t>255291</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,41%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>143475</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>143475</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>143475</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>129838</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>129838</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>129838</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>143475</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>143475</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>143475</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7374</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3830</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12005</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,15%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,89%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5186</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2470</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9898</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2538</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9611</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>6,28%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7374</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4016</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12094</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>7972</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18632</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>73238</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>68607</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>76782</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,85%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,11%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,25%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>77399</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>72687</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>80115</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>72974</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>80047</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>93,72%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,02%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,01%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>73238</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>68518</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>76596</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,85%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144565</t>
+          <t>144350</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155356</t>
+          <t>155225</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>80612</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>80612</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>80612</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>82585</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>82585</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>82585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>80612</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>80612</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>80612</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12417</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8085</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18526</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>13474</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8348</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19527</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8436</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19681</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15,01%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,76%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12417</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7942</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>19358</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19109</t>
+          <t>18322</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35458</t>
+          <t>33734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>93784</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>87675</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>98116</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>82,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,39%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76263</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>70210</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>81389</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>70056</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>81301</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>84,99%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>78,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>93784</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>86843</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>98259</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>88,31%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>160480</t>
+          <t>162204</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>176829</t>
+          <t>177616</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,65%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>106201</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>106201</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>106201</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>89737</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>89737</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>89737</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>106201</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>106201</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>106201</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>41758</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>32893</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>52758</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>38497</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29964</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>48322</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>30332</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>48868</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>10,02%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,58%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>41758</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>32162</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>53201</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66616</t>
+          <t>67069</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>95421</t>
+          <t>96012</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>528</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>371325</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>360325</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>380190</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,89%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>87,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>496</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>345705</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>335880</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>354238</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>335334</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>353870</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>89,98%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,42%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,2%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>528</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>371325</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>359882</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>380921</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>89,89%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>701864</t>
+          <t>701273</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>730669</t>
+          <t>730216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>589</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>413083</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>413083</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>413083</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>553</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>384202</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>384202</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>384202</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>413083</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>413083</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>413083</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,67 +4617,67 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3251</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6697</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,07%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4203</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1860</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8412</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1771</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8272</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,06%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>12,14%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3251</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1191</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7228</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4123</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>12624</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -4730,64 +4730,64 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>57264</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>53818</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>59295</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>94,63%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>88,93%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,98%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>65109</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>60900</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>67452</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>61040</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>67541</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,94%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>87,86%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,32%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>57264</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>53287</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>59324</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,63%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>88,06%</t>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117244</t>
+          <t>117203</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125704</t>
+          <t>125644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60515</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60515</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60515</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>69312</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>69312</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>69312</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60515</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60515</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60515</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13056</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8306</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19787</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>10,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>15,93%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>4845</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2277</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9038</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2213</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8913</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,81%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>13056</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7847</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>18909</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>10,51%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12010</t>
+          <t>12377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25211</t>
+          <t>25705</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111192</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>104461</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>115942</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>89,49%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>84,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,32%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>95884</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>91691</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>98452</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>91816</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>98516</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,19%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111192</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>105339</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>116401</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>89,49%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>199766</t>
+          <t>199272</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212967</t>
+          <t>212600</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>124248</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>124248</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>124248</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>100729</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>100729</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>100729</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>124248</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>124248</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>124248</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12661</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7868</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18879</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>19,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>11985</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7338</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17927</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7729</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>17828</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>12,53%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12661</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>7791</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>18981</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17976</t>
+          <t>18111</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33665</t>
+          <t>32981</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>82448</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>76230</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>87241</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>80,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,73%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>83679</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>77737</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>88326</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>77836</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>87935</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>87,47%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,26%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,33%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>82448</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>76128</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>87318</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>86,69%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157108</t>
+          <t>157792</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>172797</t>
+          <t>172662</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>95109</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>95109</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>95109</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>95664</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>95664</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>95664</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>95109</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>95109</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>95109</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15708</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10353</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22210</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,4%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8851</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5301</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14591</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4823</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14465</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>9,68%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,96%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15708</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>10349</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>22636</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>18,67%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17547</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33450</t>
+          <t>33070</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>68427</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>61925</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>73782</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>81,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>73,6%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87,69%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>82567</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>76827</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>86117</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>76953</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>86595</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,32%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,04%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>68427</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>61499</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>73786</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>81,33%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142103</t>
+          <t>142483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>158006</t>
+          <t>157769</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,87%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>84135</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>84135</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>84135</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>91418</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>91418</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>91418</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>84135</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>84135</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>84135</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>44676</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>34909</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>56409</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>9,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>29884</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>22450</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>38589</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>22178</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>39283</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,37%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>44676</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>35004</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>55841</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61533</t>
+          <t>63317</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89457</t>
+          <t>91117</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>319331</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>307598</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>329098</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>84,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>90,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>489</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>327238</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>318533</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>334672</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>317839</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>334944</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,63%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>89,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,71%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>319331</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>308166</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>329003</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>87,73%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>631673</t>
+          <t>630013</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>659597</t>
+          <t>657813</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>364007</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>364007</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>364007</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>537</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>357122</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>357122</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>357122</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>364007</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>364007</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>364007</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3033</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5974</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20,09%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,56%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>643</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5248</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>383</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6334</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9601</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12068</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>9127</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14046</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>79,91%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,44%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,01%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>16119</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12824</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17429</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>89,2%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>70,96%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,44%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15202</t>
+          <t>14040</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12198</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>31322</t>
+          <t>26107</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>27003</t>
+          <t>22314</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33949</t>
+          <t>28393</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18072</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18532</t>
+          <t>15765</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18532</t>
+          <t>15765</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18532</t>
+          <t>15765</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>36604</t>
+          <t>30865</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36604</t>
+          <t>30865</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36604</t>
+          <t>30865</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14755</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9862</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20587</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>27,99%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>18,71%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>39,05%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7475</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4057</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12325</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>14,84%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,06%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,48%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>17025</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11294</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23385</t>
+          <t>11141</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>24500</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17802</t>
+          <t>15731</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32370</t>
+          <t>28947</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37966</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32134</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>42859</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>72,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>60,95%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>81,29%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>42879</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>38029</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>46297</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>85,16%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,52%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>45112</t>
+          <t>38889</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38752</t>
+          <t>34592</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50843</t>
+          <t>41991</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>87991</t>
+          <t>76856</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>80121</t>
+          <t>69507</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>94689</t>
+          <t>82723</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,02%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>52721</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>52721</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>52721</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>50354</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>50354</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>50354</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62137</t>
+          <t>45733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62137</t>
+          <t>45733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62137</t>
+          <t>45733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>112491</t>
+          <t>98454</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>112491</t>
+          <t>98454</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>112491</t>
+          <t>98454</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9961</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5478</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16558</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,06%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>17156</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10627</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26230</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>25,68%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>39,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15723</t>
+          <t>22387</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>27108</t>
+          <t>25448</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19269</t>
+          <t>18496</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38748</t>
+          <t>35668</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>52058</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>45461</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>56541</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,94%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,17%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>49640</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>40566</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>56169</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>74,32%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>60,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>84,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>54775</t>
+          <t>48993</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49004</t>
+          <t>42093</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59268</t>
+          <t>54601</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>104414</t>
+          <t>101051</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>92774</t>
+          <t>90831</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>112253</t>
+          <t>108003</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>62019</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>62019</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>62019</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>66796</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>66796</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>66796</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64727</t>
+          <t>64480</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64727</t>
+          <t>64480</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64727</t>
+          <t>64480</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>131522</t>
+          <t>126499</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>131522</t>
+          <t>126499</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>131522</t>
+          <t>126499</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17682</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11083</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25785</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,61%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,41%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24,23%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>14814</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6492</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>23852</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>11,85%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17745</t>
+          <t>15882</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26047</t>
+          <t>24067</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>32558</t>
+          <t>33563</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20273</t>
+          <t>24658</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45168</t>
+          <t>45268</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>88744</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>80641</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>95343</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>75,77%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,59%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>110242</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>101204</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>118564</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>88,15%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>94,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>94748</t>
+          <t>83998</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>86446</t>
+          <t>75813</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101223</t>
+          <t>89862</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>204991</t>
+          <t>172743</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>192381</t>
+          <t>161038</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>217276</t>
+          <t>181648</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>106426</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>106426</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>106426</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>125056</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>125056</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>125056</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>112493</t>
+          <t>99880</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>112493</t>
+          <t>99880</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>112493</t>
+          <t>99880</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>237549</t>
+          <t>206306</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>237549</t>
+          <t>206306</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>237549</t>
+          <t>206306</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>45431</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>35136</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>56314</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>23,84%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>41397</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28086</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>55108</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>48051</t>
+          <t>39937</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37838</t>
+          <t>30227</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60364</t>
+          <t>51476</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>89448</t>
+          <t>85368</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70261</t>
+          <t>71378</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>107481</t>
+          <t>101591</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>190836</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>179953</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>201131</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>76,16%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>218881</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>205170</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>232192</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>84,09%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>78,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>89,21%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>209837</t>
+          <t>185920</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197524</t>
+          <t>174381</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>220050</t>
+          <t>195630</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,59%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>428719</t>
+          <t>376756</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>410686</t>
+          <t>360533</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>447906</t>
+          <t>390746</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>84,55%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>236267</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>236267</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>236267</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>260278</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>260278</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>260278</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>257888</t>
+          <t>225857</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>257888</t>
+          <t>225857</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>257888</t>
+          <t>225857</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>518167</t>
+          <t>462124</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>518167</t>
+          <t>462124</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>518167</t>
+          <t>462124</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
